--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92925936</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926082</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92925987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926203</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,8 +1419,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,51 +1215,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92926042</v>
+        <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>93345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skäppsjöbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475233</v>
+        <v>475615</v>
       </c>
       <c r="R7" t="n">
-        <v>6730900</v>
+        <v>6730561</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1289,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,75 +1313,80 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92926042</t>
+          <t>https://artportalen.se/Sighting/135886116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>92926094</v>
+        <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>93345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäppsjöbodarna, Dlr</t>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475233</v>
+        <v>475199</v>
       </c>
       <c r="R8" t="n">
-        <v>6730900</v>
+        <v>6730554</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,12 +1410,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,25 +1434,8216 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135889241</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135886456</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>475289</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6730599</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886456</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135886596</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>475285</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6730662</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886596</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135890022</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>475429</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6730350</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135891144</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475608</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6730345</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891144</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>92926042</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475233</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6730900</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92926042</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>92926094</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475233</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6730900</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/92926094</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135885083</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475615</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6730561</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885083</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135885329</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475602</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6730487</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885329</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135885340</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475589</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6730489</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885340</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135885531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>475496</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6730499</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885531</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135885690</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>475446</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6730548</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885690</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135885718</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>475445</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6730550</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885718</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135885778</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>475424</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6730570</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885778</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135886466</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>475289</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6730598</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886466</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135889165</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>475200</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6730652</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889165</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135889395</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475288</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6730507</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889395</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135890519</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>475444</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6730390</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890519</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135891118</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>475598</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6730347</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891118</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135891289</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>475630</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6730381</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891289</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135885035</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>475608</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6730566</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885035</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135885312</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>475609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6730492</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885312</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135885307</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>475610</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6730495</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885307</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135885227</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>475603</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6730466</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885227</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135887218</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>475270</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6730865</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Födosök gammal tall längstner</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887218</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135891017</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>475569</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6730330</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891017</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135886448</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>475284</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6730583</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886448</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135886883</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>475205</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6730808</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack Hålen syns ingen kåda</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886883</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135886981</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>475233</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6730811</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack Tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886981</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135887115</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>475234</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6730859</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack kåda</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887115</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135887235</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>475291</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6730867</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack kåda längst ner gran foto</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887235</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135887424</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>475289</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6730947</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack Tall Kåda Foto</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887424</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135888552</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>475313</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6730928</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhach. Hela granen</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888552</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135888618</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>475226</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6730942</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack Gran Kåda Foto</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888618</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135888685</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>475215</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6730960</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack Gran kåda Foto</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888685</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135889020</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>475193</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6730828</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889020</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135889076</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>475204</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6730686</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack Tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889076</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135889132</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>475200</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6730652</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre i Tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889132</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135889637</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>475309</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6730483</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889637</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135891351</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>475630</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6730379</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891351</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135885199</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>475590</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6730454</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sandbad foto</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885199</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135885372</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>475573</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6730540</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Sandbad foto</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885372</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135885405</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>475544</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6730532</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885405</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135885503</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>475497</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6730496</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885503</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135885643</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>475453</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6730553</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885643</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135885739</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>475445</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6730557</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885739</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135885764</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>475425</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6730571</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885764</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135886638</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>475305</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6730668</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Under betade tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886638</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135888935</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>475087</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6730885</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888935</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135889050</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>475223</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6730667</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889050</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135889091</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>475205</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6730678</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889091</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135889183</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>475196</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6730644</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889183</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135889204</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>475207</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6730609</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889204</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135889313</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6730538</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889313</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135889328</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6730539</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889328</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135889434</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>475287</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6730508</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889434</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135889458</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>475285</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6730508</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889458</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135889661</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>475310</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6730471</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889661</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135889712</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>475314</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6730409</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889712</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135889739</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>475346</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6730415</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889739</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135890060</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>475464</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6730382</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890060</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135890316</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>475437</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6730399</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890316</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135890654</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>475434</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6730369</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890654</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135890678</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>475436</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6730365</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890678</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135891066</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>475572</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6730352</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891066</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135891196</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>475615</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6730357</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891196</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135891212</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>475625</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6730356</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891212</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135885517</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>475497</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6730497</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885517</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135885567</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>475491</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6730502</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885567</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135885669</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>475450</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6730551</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135885669</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135889269</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skäppsjöbodarna, Skäppsjöbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6730538</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889269</t>
         </is>
       </c>
     </row>
@@ -1434,6 +9656,76 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135885517</v>
       </c>
       <c r="B75" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>135885567</v>
       </c>
       <c r="B76" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>135885669</v>
       </c>
       <c r="B77" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135889269</v>
       </c>
       <c r="B78" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135885227</v>
       </c>
       <c r="B31" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135887218</v>
       </c>
       <c r="B32" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135891017</v>
       </c>
       <c r="B33" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>135886448</v>
       </c>
       <c r="B34" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>135886883</v>
       </c>
       <c r="B35" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135886981</v>
       </c>
       <c r="B36" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>135887115</v>
       </c>
       <c r="B37" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135887235</v>
       </c>
       <c r="B38" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>135887424</v>
       </c>
       <c r="B39" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>135888552</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>135888618</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>135888685</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>135889020</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135889076</v>
       </c>
       <c r="B44" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135889132</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135889637</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>135891351</v>
       </c>
       <c r="B47" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>135885199</v>
       </c>
       <c r="B48" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>135885372</v>
       </c>
       <c r="B49" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135885405</v>
       </c>
       <c r="B50" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>135885503</v>
       </c>
       <c r="B51" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135885643</v>
       </c>
       <c r="B52" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135885739</v>
       </c>
       <c r="B53" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>135885764</v>
       </c>
       <c r="B54" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135886638</v>
       </c>
       <c r="B55" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>135888935</v>
       </c>
       <c r="B56" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135889050</v>
       </c>
       <c r="B57" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135889091</v>
       </c>
       <c r="B58" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135889183</v>
       </c>
       <c r="B59" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135889204</v>
       </c>
       <c r="B60" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135889313</v>
       </c>
       <c r="B61" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135889328</v>
       </c>
       <c r="B62" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135889434</v>
       </c>
       <c r="B63" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135889458</v>
       </c>
       <c r="B64" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135889661</v>
       </c>
       <c r="B65" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135889712</v>
       </c>
       <c r="B66" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>135889739</v>
       </c>
       <c r="B67" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>135890060</v>
       </c>
       <c r="B68" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>135890316</v>
       </c>
       <c r="B69" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>135890654</v>
       </c>
       <c r="B70" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>135890678</v>
       </c>
       <c r="B71" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135891066</v>
       </c>
       <c r="B72" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135891196</v>
       </c>
       <c r="B73" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>135891212</v>
       </c>
       <c r="B74" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 4553-2026 artfynd.xlsx
+++ b/artfynd/A 4553-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>135886116</v>
       </c>
       <c r="B7" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135889241</v>
       </c>
       <c r="B8" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135886456</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135886596</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>135890022</v>
       </c>
       <c r="B11" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135891144</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135885083</v>
       </c>
       <c r="B15" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135885329</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>135885340</v>
       </c>
       <c r="B17" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135885531</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135885690</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>135885718</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135885778</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135886466</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135889165</v>
       </c>
       <c r="B23" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>135889395</v>
       </c>
       <c r="B24" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135890519</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>135891118</v>
       </c>
       <c r="B26" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135891289</v>
       </c>
       <c r="B27" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>135885035</v>
       </c>
       <c r="B28" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>135885312</v>
       </c>
       <c r="B29" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135885307</v>
       </c>
       <c r="B30" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
